--- a/ultimate_report.xlsx
+++ b/ultimate_report.xlsx
@@ -59,9 +59,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/ultimate_report.xlsx
+++ b/ultimate_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -434,7 +434,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +472,56 @@
         <is>
           <t>avg_ppsf</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>201.5151515151515</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>575000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>198.2142857142857</v>
       </c>
     </row>
   </sheetData>

--- a/ultimate_report.xlsx
+++ b/ultimate_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -434,7 +434,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,56 +472,6 @@
         <is>
           <t>avg_ppsf</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>450000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>201.5151515151515</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>575000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>550000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>198.2142857142857</v>
       </c>
     </row>
   </sheetData>
